--- a/output/2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,6 @@
           <t>Canal System (Chiaramonte Domenico)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Palermo (PA)</t>
@@ -606,7 +605,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -643,7 +642,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -680,7 +679,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -717,7 +716,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -754,7 +753,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -791,7 +790,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
